--- a/output/yearly_benthic_cover_iteration_10_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_10_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.274138008622</v>
+        <v>45.36076432374028</v>
       </c>
       <c r="M2" t="n">
-        <v>99.4698199234092</v>
+        <v>100.3071404910819</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.00216103239887</v>
+        <v>87.99758608809707</v>
       </c>
       <c r="C3" t="n">
-        <v>45.92162921614064</v>
+        <v>45.93002261359656</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228671440058053</v>
+        <v>2.228653330204135</v>
       </c>
       <c r="E3" t="n">
-        <v>5.700922277263319</v>
+        <v>5.705424611229269</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428904800193509</v>
+        <v>0.7428844434013784</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97094226722098</v>
+        <v>33.97391172105822</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17296208089014</v>
+        <v>34.1726843964634</v>
       </c>
       <c r="I3" t="n">
-        <v>6.542706986826084</v>
+        <v>6.530999814482062</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643065500120943</v>
+        <v>4.643027771258614</v>
       </c>
       <c r="K3" t="n">
-        <v>11.99783896760114</v>
+        <v>12.00241391190293</v>
       </c>
       <c r="L3" t="n">
-        <v>48.84567595121764</v>
+        <v>48.83312594306501</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7651441349594</v>
+        <v>106.7655624685645</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.07035989702777</v>
+        <v>87.03831081957094</v>
       </c>
       <c r="C4" t="n">
-        <v>42.62033463291645</v>
+        <v>42.59868214493383</v>
       </c>
       <c r="D4" t="n">
-        <v>2.183667305714999</v>
+        <v>2.182187783762338</v>
       </c>
       <c r="E4" t="n">
-        <v>6.496412109622484</v>
+        <v>6.49544922795488</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444443578599698</v>
+        <v>0.744436094734511</v>
       </c>
       <c r="G4" t="n">
-        <v>33.2849583119035</v>
+        <v>33.26558425195843</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24444046155861</v>
+        <v>34.2440603577875</v>
       </c>
       <c r="I4" t="n">
-        <v>5.463660113743382</v>
+        <v>5.4538675112826</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652777236624811</v>
+        <v>4.652725592090693</v>
       </c>
       <c r="K4" t="n">
-        <v>12.92964010297224</v>
+        <v>12.96168918042905</v>
       </c>
       <c r="L4" t="n">
-        <v>44.26828340336615</v>
+        <v>44.25821201312373</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81825813925484</v>
+        <v>99.81858333848662</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.86983112939119</v>
+        <v>85.84713141848449</v>
       </c>
       <c r="C5" t="n">
-        <v>42.26779499992872</v>
+        <v>42.25395955611294</v>
       </c>
       <c r="D5" t="n">
-        <v>2.124953008693165</v>
+        <v>2.12396227413938</v>
       </c>
       <c r="E5" t="n">
-        <v>7.081922277120944</v>
+        <v>7.080957241281508</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457624357320387</v>
+        <v>0.7457521399276794</v>
       </c>
       <c r="G5" t="n">
-        <v>32.38999463150686</v>
+        <v>32.37798621370148</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30507204367378</v>
+        <v>34.30459843667325</v>
       </c>
       <c r="I5" t="n">
-        <v>4.561111509339161</v>
+        <v>4.552924238213207</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661015223325242</v>
+        <v>4.660950874547996</v>
       </c>
       <c r="K5" t="n">
-        <v>14.13016887060883</v>
+        <v>14.15286858151551</v>
       </c>
       <c r="L5" t="n">
-        <v>43.45026779296957</v>
+        <v>43.44167554261369</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84823166350711</v>
+        <v>99.84850368024215</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.47840070912001</v>
+        <v>84.36042367403014</v>
       </c>
       <c r="C6" t="n">
-        <v>41.58468964241228</v>
+        <v>41.47430071323642</v>
       </c>
       <c r="D6" t="n">
-        <v>2.05695750591768</v>
+        <v>2.05109948619096</v>
       </c>
       <c r="E6" t="n">
-        <v>7.489749958639757</v>
+        <v>7.471344138477821</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468825822604469</v>
+        <v>0.746871823344529</v>
       </c>
       <c r="G6" t="n">
-        <v>31.35356043232473</v>
+        <v>31.26725540063103</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35659878398056</v>
+        <v>34.35610387384833</v>
       </c>
       <c r="I6" t="n">
-        <v>3.806635306869039</v>
+        <v>3.799800055634172</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668016139127793</v>
+        <v>4.667948895903305</v>
       </c>
       <c r="K6" t="n">
-        <v>15.52159929087999</v>
+        <v>15.63957632596985</v>
       </c>
       <c r="L6" t="n">
-        <v>42.76701352478166</v>
+        <v>42.75965284306558</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87330245807392</v>
+        <v>99.87352988227185</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.92495281477541</v>
+        <v>82.62685703820981</v>
       </c>
       <c r="C7" t="n">
-        <v>40.62240193297428</v>
+        <v>40.33075422055097</v>
       </c>
       <c r="D7" t="n">
-        <v>1.981357941154869</v>
+        <v>1.966439523664011</v>
       </c>
       <c r="E7" t="n">
-        <v>7.743852797848277</v>
+        <v>7.691386414865234</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478361685609274</v>
+        <v>0.7478271199211234</v>
       </c>
       <c r="G7" t="n">
-        <v>30.20121989265434</v>
+        <v>29.97668676251304</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40046375380266</v>
+        <v>34.40004751637167</v>
       </c>
       <c r="I7" t="n">
-        <v>3.176246207248544</v>
+        <v>3.170550201367698</v>
       </c>
       <c r="J7" t="n">
-        <v>4.673976053505795</v>
+        <v>4.67391949950702</v>
       </c>
       <c r="K7" t="n">
-        <v>17.07504718522459</v>
+        <v>17.3731429617902</v>
       </c>
       <c r="L7" t="n">
-        <v>42.19681101216588</v>
+        <v>42.19055281611345</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89426013036474</v>
+        <v>99.8944499984546</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.95257702887054</v>
+        <v>87.60255139647546</v>
       </c>
       <c r="C8" t="n">
-        <v>42.99350386686686</v>
+        <v>42.6819770626727</v>
       </c>
       <c r="D8" t="n">
-        <v>1.985643529291967</v>
+        <v>1.970682221236212</v>
       </c>
       <c r="E8" t="n">
-        <v>9.627167167051818</v>
+        <v>9.559392128151408</v>
       </c>
       <c r="F8" t="n">
-        <v>0.749453704567879</v>
+        <v>0.7494405965970824</v>
       </c>
       <c r="G8" t="n">
-        <v>30.72423248166276</v>
+        <v>30.49455074605157</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47487041012243</v>
+        <v>34.47426744346578</v>
       </c>
       <c r="I8" t="n">
-        <v>5.70712408262443</v>
+        <v>5.670214532241639</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684085653549243</v>
+        <v>4.684003728731764</v>
       </c>
       <c r="K8" t="n">
-        <v>12.04742297112946</v>
+        <v>12.39744860352455</v>
       </c>
       <c r="L8" t="n">
-        <v>44.76924627959416</v>
+        <v>44.73197409774068</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81017311759048</v>
+        <v>99.81139976393793</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.05080688435662</v>
+        <v>85.41785430534121</v>
       </c>
       <c r="C9" t="n">
-        <v>41.97738286064723</v>
+        <v>41.3768983970467</v>
       </c>
       <c r="D9" t="n">
-        <v>1.899949155649333</v>
+        <v>1.871685391908144</v>
       </c>
       <c r="E9" t="n">
-        <v>10.00580685430477</v>
+        <v>9.868162608045317</v>
       </c>
       <c r="F9" t="n">
-        <v>0.750836969973196</v>
+        <v>0.7508250779221286</v>
       </c>
       <c r="G9" t="n">
-        <v>29.3982674636086</v>
+        <v>28.96266305603665</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53850061876702</v>
+        <v>34.53795358441791</v>
       </c>
       <c r="I9" t="n">
-        <v>4.76471475972122</v>
+        <v>4.733907849997754</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692731062332475</v>
+        <v>4.692656737013303</v>
       </c>
       <c r="K9" t="n">
-        <v>13.94919311564339</v>
+        <v>14.58214569465878</v>
       </c>
       <c r="L9" t="n">
-        <v>43.91489279919203</v>
+        <v>43.88344994906559</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84146877548264</v>
+        <v>99.84249404077107</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.89605801298421</v>
+        <v>83.03349788848085</v>
       </c>
       <c r="C10" t="n">
-        <v>40.56187751101371</v>
+        <v>39.72646691844048</v>
       </c>
       <c r="D10" t="n">
-        <v>1.803678037613324</v>
+        <v>1.764836823488972</v>
       </c>
       <c r="E10" t="n">
-        <v>10.16162054512126</v>
+        <v>9.963350672369877</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520233509562111</v>
+        <v>0.7520160211479771</v>
       </c>
       <c r="G10" t="n">
-        <v>27.90864650789625</v>
+        <v>27.30927670247355</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59307414398572</v>
+        <v>34.59273697280693</v>
       </c>
       <c r="I10" t="n">
-        <v>3.976869483935135</v>
+        <v>3.951180564018697</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700145943476318</v>
+        <v>4.700100132174856</v>
       </c>
       <c r="K10" t="n">
-        <v>16.10394198701576</v>
+        <v>16.96650211151913</v>
       </c>
       <c r="L10" t="n">
-        <v>43.20182731420052</v>
+        <v>43.17553352976267</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86764681222999</v>
+        <v>99.86850255972229</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.65726788607479</v>
+        <v>80.51111647518992</v>
       </c>
       <c r="C11" t="n">
-        <v>38.93952129855747</v>
+        <v>37.81587388452537</v>
       </c>
       <c r="D11" t="n">
-        <v>1.704713673647893</v>
+        <v>1.65305648537321</v>
       </c>
       <c r="E11" t="n">
-        <v>10.15716308590055</v>
+        <v>9.88182123444858</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530420906866107</v>
+        <v>0.7530425899608026</v>
       </c>
       <c r="G11" t="n">
-        <v>26.37735245585761</v>
+        <v>25.57957560893873</v>
       </c>
       <c r="H11" t="n">
-        <v>34.6399361715841</v>
+        <v>34.63995913819691</v>
       </c>
       <c r="I11" t="n">
-        <v>3.318547341606723</v>
+        <v>3.297145231016675</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706513066791316</v>
+        <v>4.706516187255017</v>
       </c>
       <c r="K11" t="n">
-        <v>18.34273211392521</v>
+        <v>19.48888352481007</v>
       </c>
       <c r="L11" t="n">
-        <v>42.60727799074131</v>
+        <v>42.58548757499737</v>
       </c>
       <c r="M11" t="n">
-        <v>99.88953140322398</v>
+        <v>99.89024498433281</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>79.23893765041197</v>
+        <v>77.99556887601895</v>
       </c>
       <c r="C12" t="n">
-        <v>37.03485042343076</v>
+        <v>35.80988515719157</v>
       </c>
       <c r="D12" t="n">
-        <v>1.598763859837708</v>
+        <v>1.542827122597687</v>
       </c>
       <c r="E12" t="n">
-        <v>9.987330495761409</v>
+        <v>9.681355343562425</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539191554238348</v>
+        <v>0.7539279001479801</v>
       </c>
       <c r="G12" t="n">
-        <v>24.73797123618132</v>
+        <v>23.87387447628502</v>
       </c>
       <c r="H12" t="n">
-        <v>34.68028114949641</v>
+        <v>34.68068340680708</v>
       </c>
       <c r="I12" t="n">
-        <v>2.768677032312307</v>
+        <v>2.75085125069389</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711994721398967</v>
+        <v>4.712049375924876</v>
       </c>
       <c r="K12" t="n">
-        <v>20.76106234958805</v>
+        <v>22.00443112398102</v>
       </c>
       <c r="L12" t="n">
-        <v>42.11190535638102</v>
+        <v>42.09409635129916</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90781812939981</v>
+        <v>99.90841263247177</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76.7836464033559</v>
+        <v>75.44850799913188</v>
       </c>
       <c r="C13" t="n">
-        <v>35.00723197685826</v>
+        <v>33.68698663941351</v>
       </c>
       <c r="D13" t="n">
-        <v>1.492191513981197</v>
+        <v>1.43231499926237</v>
       </c>
       <c r="E13" t="n">
-        <v>9.706506895143301</v>
+        <v>9.370333531924118</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546750496998065</v>
+        <v>0.7546922352975829</v>
       </c>
       <c r="G13" t="n">
-        <v>23.08895746210316</v>
+        <v>22.16379787601575</v>
       </c>
       <c r="H13" t="n">
-        <v>34.7150522861911</v>
+        <v>34.7158428236888</v>
       </c>
       <c r="I13" t="n">
-        <v>2.309544135613547</v>
+        <v>2.294700062333369</v>
       </c>
       <c r="J13" t="n">
-        <v>4.71671906062379</v>
+        <v>4.716826470609893</v>
       </c>
       <c r="K13" t="n">
-        <v>23.2163535966441</v>
+        <v>24.55149200086811</v>
       </c>
       <c r="L13" t="n">
-        <v>41.69950673115563</v>
+        <v>41.68510882497687</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92309230465798</v>
+        <v>99.92358746525849</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.52503652063118</v>
+        <v>82.64990661706558</v>
       </c>
       <c r="C14" t="n">
-        <v>39.19635540243348</v>
+        <v>38.14992921436832</v>
       </c>
       <c r="D14" t="n">
-        <v>1.493961260754371</v>
+        <v>1.434051864536537</v>
       </c>
       <c r="E14" t="n">
-        <v>12.04514725196835</v>
+        <v>11.84933576198753</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555700981714588</v>
+        <v>0.7556073962341415</v>
       </c>
       <c r="G14" t="n">
-        <v>24.94816386966816</v>
+        <v>24.15719586400654</v>
       </c>
       <c r="H14" t="n">
-        <v>36.58804730172416</v>
+        <v>36.72446177285129</v>
       </c>
       <c r="I14" t="n">
-        <v>2.971833624773053</v>
+        <v>3.006707730986146</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722313113571617</v>
+        <v>4.722546226463384</v>
       </c>
       <c r="K14" t="n">
-        <v>16.47496347936883</v>
+        <v>17.35009338293444</v>
       </c>
       <c r="L14" t="n">
-        <v>44.22973734519314</v>
+        <v>44.39987519840025</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90105622699545</v>
+        <v>99.899897795703</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.68414997698969</v>
+        <v>81.84283146435834</v>
       </c>
       <c r="C15" t="n">
-        <v>38.80745221900149</v>
+        <v>37.80671403002783</v>
       </c>
       <c r="D15" t="n">
-        <v>1.461934882616722</v>
+        <v>1.404572565216016</v>
       </c>
       <c r="E15" t="n">
-        <v>12.20736557849086</v>
+        <v>12.02377802380568</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7563252048285383</v>
+        <v>0.7563792724990538</v>
       </c>
       <c r="G15" t="n">
-        <v>24.42061020210837</v>
+        <v>23.6606048931844</v>
       </c>
       <c r="H15" t="n">
-        <v>36.63187854912034</v>
+        <v>36.76197694346161</v>
       </c>
       <c r="I15" t="n">
-        <v>2.479003029646497</v>
+        <v>2.508149313072486</v>
       </c>
       <c r="J15" t="n">
-        <v>4.727032530178364</v>
+        <v>4.727370453119086</v>
       </c>
       <c r="K15" t="n">
-        <v>17.31585002301031</v>
+        <v>18.15716853564166</v>
       </c>
       <c r="L15" t="n">
-        <v>43.79414682396671</v>
+        <v>43.95259777513647</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91744906597852</v>
+        <v>99.91648034080596</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.13072237301417</v>
+        <v>79.3011750153567</v>
       </c>
       <c r="C16" t="n">
-        <v>36.63711424040876</v>
+        <v>35.6520323769636</v>
       </c>
       <c r="D16" t="n">
-        <v>1.36510449126779</v>
+        <v>1.30946953547513</v>
       </c>
       <c r="E16" t="n">
-        <v>11.74342006115381</v>
+        <v>11.55831335753711</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7569757200282805</v>
+        <v>0.7570443811616964</v>
       </c>
       <c r="G16" t="n">
-        <v>22.80312554464034</v>
+        <v>22.05855508346324</v>
       </c>
       <c r="H16" t="n">
-        <v>36.66338562258449</v>
+        <v>36.79430293415168</v>
       </c>
       <c r="I16" t="n">
-        <v>2.067612683162712</v>
+        <v>2.091962341307272</v>
       </c>
       <c r="J16" t="n">
-        <v>4.731098250176752</v>
+        <v>4.731527382260602</v>
       </c>
       <c r="K16" t="n">
-        <v>19.86927762698584</v>
+        <v>20.69882498464327</v>
       </c>
       <c r="L16" t="n">
-        <v>43.42474693733745</v>
+        <v>43.5794718241411</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93113880473204</v>
+        <v>99.93032918574798</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.82965641016737</v>
+        <v>81.22852247338</v>
       </c>
       <c r="C17" t="n">
-        <v>37.86890496776552</v>
+        <v>37.03942782956093</v>
       </c>
       <c r="D17" t="n">
-        <v>1.36625632126181</v>
+        <v>1.310593436171168</v>
       </c>
       <c r="E17" t="n">
-        <v>12.52658761380338</v>
+        <v>12.42113184663555</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7576144310900714</v>
+        <v>0.7576941425222088</v>
       </c>
       <c r="G17" t="n">
-        <v>23.25039913041782</v>
+        <v>22.58179886410201</v>
       </c>
       <c r="H17" t="n">
-        <v>37.122354037135</v>
+        <v>37.33019421579554</v>
       </c>
       <c r="I17" t="n">
-        <v>2.071354682146332</v>
+        <v>2.091521577389706</v>
       </c>
       <c r="J17" t="n">
-        <v>4.735090194312946</v>
+        <v>4.735588390763804</v>
       </c>
       <c r="K17" t="n">
-        <v>18.17034358983265</v>
+        <v>18.77147752662001</v>
       </c>
       <c r="L17" t="n">
-        <v>43.8917644952333</v>
+        <v>44.11943704411923</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93101305283147</v>
+        <v>99.93034240030018</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.3088424649269</v>
+        <v>78.77332854469141</v>
       </c>
       <c r="C18" t="n">
-        <v>35.66773170163073</v>
+        <v>34.90651346871314</v>
       </c>
       <c r="D18" t="n">
-        <v>1.274456711419823</v>
+        <v>1.22288481065303</v>
       </c>
       <c r="E18" t="n">
-        <v>11.97281543680832</v>
+        <v>11.88057802674039</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7581644704737096</v>
+        <v>0.7582533783741631</v>
       </c>
       <c r="G18" t="n">
-        <v>21.68819038845085</v>
+        <v>21.07056091232062</v>
       </c>
       <c r="H18" t="n">
-        <v>37.14930542018139</v>
+        <v>37.35774673572976</v>
       </c>
       <c r="I18" t="n">
-        <v>1.727382097132122</v>
+        <v>1.744221066034921</v>
       </c>
       <c r="J18" t="n">
-        <v>4.738527940460684</v>
+        <v>4.739083614838519</v>
       </c>
       <c r="K18" t="n">
-        <v>20.6911575350731</v>
+        <v>21.2266714553086</v>
       </c>
       <c r="L18" t="n">
-        <v>43.58357313323656</v>
+        <v>43.80871725438409</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94246236994039</v>
+        <v>99.94190217840583</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.29597335845548</v>
+        <v>77.85747574635361</v>
       </c>
       <c r="C19" t="n">
-        <v>34.92067208083851</v>
+        <v>34.25627633703635</v>
       </c>
       <c r="D19" t="n">
-        <v>1.238265784116556</v>
+        <v>1.190754309997598</v>
       </c>
       <c r="E19" t="n">
-        <v>11.87288300431438</v>
+        <v>11.81121509039416</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7586293882464055</v>
+        <v>0.7587262872994786</v>
       </c>
       <c r="G19" t="n">
-        <v>21.07230778164704</v>
+        <v>20.51694566965348</v>
       </c>
       <c r="H19" t="n">
-        <v>37.17208592890447</v>
+        <v>37.38104608706121</v>
       </c>
       <c r="I19" t="n">
-        <v>1.440367794686593</v>
+        <v>1.456749006325947</v>
       </c>
       <c r="J19" t="n">
-        <v>4.741433676540034</v>
+        <v>4.742039295621741</v>
       </c>
       <c r="K19" t="n">
-        <v>21.70402664154453</v>
+        <v>22.14252425364637</v>
       </c>
       <c r="L19" t="n">
-        <v>43.32731844158551</v>
+        <v>43.5526713751641</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95201716396855</v>
+        <v>99.95147196584682</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>75.61902225833163</v>
+        <v>75.25137737804525</v>
       </c>
       <c r="C20" t="n">
-        <v>32.46518594079588</v>
+        <v>31.87386923991496</v>
       </c>
       <c r="D20" t="n">
-        <v>1.141899756440551</v>
+        <v>1.098763908801978</v>
       </c>
       <c r="E20" t="n">
-        <v>11.14905211415717</v>
+        <v>11.10118789897859</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7590309934706796</v>
+        <v>0.7591344999931137</v>
       </c>
       <c r="G20" t="n">
-        <v>19.43238958239528</v>
+        <v>18.93193182791146</v>
       </c>
       <c r="H20" t="n">
-        <v>37.19176418568901</v>
+        <v>37.4011579742721</v>
       </c>
       <c r="I20" t="n">
-        <v>1.200941916987176</v>
+        <v>1.214610643131059</v>
       </c>
       <c r="J20" t="n">
-        <v>4.743943709191747</v>
+        <v>4.74459062495696</v>
       </c>
       <c r="K20" t="n">
-        <v>24.38097774166839</v>
+        <v>24.74862262195474</v>
       </c>
       <c r="L20" t="n">
-        <v>43.11382610101666</v>
+        <v>43.33704288795458</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95998978348094</v>
+        <v>99.95953474982427</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.72268518031262</v>
+        <v>81.4727125798573</v>
       </c>
       <c r="C21" t="n">
-        <v>36.26291233026577</v>
+        <v>35.76002914789593</v>
       </c>
       <c r="D21" t="n">
-        <v>1.142701328943332</v>
+        <v>1.099536922464264</v>
       </c>
       <c r="E21" t="n">
-        <v>13.1918911447785</v>
+        <v>13.18816070727399</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7595638058911161</v>
+        <v>0.7596685740879273</v>
       </c>
       <c r="G21" t="n">
-        <v>21.19421130907702</v>
+        <v>20.73782120679901</v>
       </c>
       <c r="H21" t="n">
-        <v>38.96605235372717</v>
+        <v>39.22004101269707</v>
       </c>
       <c r="I21" t="n">
-        <v>1.720991451076014</v>
+        <v>1.719555568485502</v>
       </c>
       <c r="J21" t="n">
-        <v>4.747273786819474</v>
+        <v>4.747928588049545</v>
       </c>
       <c r="K21" t="n">
-        <v>18.27731481968738</v>
+        <v>18.5272874201427</v>
       </c>
       <c r="L21" t="n">
-        <v>45.40244670923054</v>
+        <v>45.65540520997445</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94267385918369</v>
+        <v>99.94272177801307</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_10_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_10_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.36076432374028</v>
+        <v>45.24654833930718</v>
       </c>
       <c r="M2" t="n">
-        <v>100.3071404910819</v>
+        <v>99.56538375461344</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.99758608809707</v>
+        <v>88.04043937538745</v>
       </c>
       <c r="C3" t="n">
-        <v>45.93002261359656</v>
+        <v>45.93622173675656</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228653330204135</v>
+        <v>2.228758577077292</v>
       </c>
       <c r="E3" t="n">
-        <v>5.705424611229269</v>
+        <v>5.711361967982151</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428844434013784</v>
+        <v>0.7429195256924307</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97391172105822</v>
+        <v>33.97560501021501</v>
       </c>
       <c r="H3" t="n">
-        <v>34.1726843964634</v>
+        <v>34.17429818185181</v>
       </c>
       <c r="I3" t="n">
-        <v>6.530999814482062</v>
+        <v>6.564249076991062</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643027771258614</v>
+        <v>4.643247035577692</v>
       </c>
       <c r="K3" t="n">
-        <v>12.00241391190293</v>
+        <v>11.95956062461255</v>
       </c>
       <c r="L3" t="n">
-        <v>48.83312594306501</v>
+        <v>48.86859771480408</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7655624685645</v>
+        <v>106.7643800761732</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.03831081957094</v>
+        <v>87.15020295939433</v>
       </c>
       <c r="C4" t="n">
-        <v>42.59868214493383</v>
+        <v>42.68010992566696</v>
       </c>
       <c r="D4" t="n">
-        <v>2.182187783762338</v>
+        <v>2.18599625133962</v>
       </c>
       <c r="E4" t="n">
-        <v>6.49544922795488</v>
+        <v>6.515393052263231</v>
       </c>
       <c r="F4" t="n">
-        <v>0.744436094734511</v>
+        <v>0.7444771600807732</v>
       </c>
       <c r="G4" t="n">
-        <v>33.26558425195843</v>
+        <v>33.32372826433323</v>
       </c>
       <c r="H4" t="n">
-        <v>34.2440603577875</v>
+        <v>34.24594936371557</v>
       </c>
       <c r="I4" t="n">
-        <v>5.4538675112826</v>
+        <v>5.481676617157071</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652725592090693</v>
+        <v>4.652982250504833</v>
       </c>
       <c r="K4" t="n">
-        <v>12.96168918042905</v>
+        <v>12.84979704060568</v>
       </c>
       <c r="L4" t="n">
-        <v>44.25821201312373</v>
+        <v>44.28775278158872</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81858333848662</v>
+        <v>99.81765974786136</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.84713141848449</v>
+        <v>85.99652855293651</v>
       </c>
       <c r="C5" t="n">
-        <v>42.25395955611294</v>
+        <v>42.3772642961642</v>
       </c>
       <c r="D5" t="n">
-        <v>2.12396227413938</v>
+        <v>2.129757267497589</v>
       </c>
       <c r="E5" t="n">
-        <v>7.080957241281508</v>
+        <v>7.110466388594553</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457521399276794</v>
+        <v>0.7457976984642514</v>
       </c>
       <c r="G5" t="n">
-        <v>32.37798621370148</v>
+        <v>32.46641086762424</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30459843667325</v>
+        <v>34.30669412935556</v>
       </c>
       <c r="I5" t="n">
-        <v>4.552924238213207</v>
+        <v>4.576166585998744</v>
       </c>
       <c r="J5" t="n">
-        <v>4.660950874547996</v>
+        <v>4.661235615401571</v>
       </c>
       <c r="K5" t="n">
-        <v>14.15286858151551</v>
+        <v>14.00347144706348</v>
       </c>
       <c r="L5" t="n">
-        <v>43.44167554261369</v>
+        <v>43.4669954618513</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84850368024215</v>
+        <v>99.84773120507899</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.36042367403014</v>
+        <v>84.66295688564968</v>
       </c>
       <c r="C6" t="n">
-        <v>41.47430071323642</v>
+        <v>41.75443924739364</v>
       </c>
       <c r="D6" t="n">
-        <v>2.05109948619096</v>
+        <v>2.064758271034725</v>
       </c>
       <c r="E6" t="n">
-        <v>7.471344138477821</v>
+        <v>7.529993351334759</v>
       </c>
       <c r="F6" t="n">
-        <v>0.746871823344529</v>
+        <v>0.7469191473541587</v>
       </c>
       <c r="G6" t="n">
-        <v>31.26725540063103</v>
+        <v>31.47555422994453</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35610387384833</v>
+        <v>34.3582807782913</v>
       </c>
       <c r="I6" t="n">
-        <v>3.799800055634172</v>
+        <v>3.819206436726723</v>
       </c>
       <c r="J6" t="n">
-        <v>4.667948895903305</v>
+        <v>4.668244670963491</v>
       </c>
       <c r="K6" t="n">
-        <v>15.63957632596985</v>
+        <v>15.3370431143503</v>
       </c>
       <c r="L6" t="n">
-        <v>42.75965284306558</v>
+        <v>42.78140189975609</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87352988227185</v>
+        <v>99.87288426150005</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.62685703820981</v>
+        <v>83.08793117410553</v>
       </c>
       <c r="C7" t="n">
-        <v>40.33075422055097</v>
+        <v>40.77264462655828</v>
       </c>
       <c r="D7" t="n">
-        <v>1.966439523664011</v>
+        <v>1.988114304554906</v>
       </c>
       <c r="E7" t="n">
-        <v>7.691386414865234</v>
+        <v>7.781602981770919</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478271199211234</v>
+        <v>0.7478740545238338</v>
       </c>
       <c r="G7" t="n">
-        <v>29.97668676251304</v>
+        <v>30.30717953099023</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40004751637167</v>
+        <v>34.40220650809636</v>
       </c>
       <c r="I7" t="n">
-        <v>3.170550201367698</v>
+        <v>3.186740953395325</v>
       </c>
       <c r="J7" t="n">
-        <v>4.67391949950702</v>
+        <v>4.674212840773961</v>
       </c>
       <c r="K7" t="n">
-        <v>17.3731429617902</v>
+        <v>16.91206882589447</v>
       </c>
       <c r="L7" t="n">
-        <v>42.19055281611345</v>
+        <v>42.20919747986039</v>
       </c>
       <c r="M7" t="n">
-        <v>99.8944499984546</v>
+        <v>99.89391093231313</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.60255139647546</v>
+        <v>88.00852151280802</v>
       </c>
       <c r="C8" t="n">
-        <v>42.6819770626727</v>
+        <v>43.09981302519947</v>
       </c>
       <c r="D8" t="n">
-        <v>1.970682221236212</v>
+        <v>1.992373458864608</v>
       </c>
       <c r="E8" t="n">
-        <v>9.559392128151408</v>
+        <v>9.632453256509477</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494405965970824</v>
+        <v>0.7494762315189604</v>
       </c>
       <c r="G8" t="n">
-        <v>30.49455074605157</v>
+        <v>30.81784317704882</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47426744346578</v>
+        <v>34.47590664987217</v>
       </c>
       <c r="I8" t="n">
-        <v>5.670214532241639</v>
+        <v>5.656242292000476</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684003728731764</v>
+        <v>4.684226446993502</v>
       </c>
       <c r="K8" t="n">
-        <v>12.39744860352455</v>
+        <v>11.99147848719198</v>
       </c>
       <c r="L8" t="n">
-        <v>44.73197409774068</v>
+        <v>44.72057012829442</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81139976393793</v>
+        <v>99.81186164068586</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.41785430534121</v>
+        <v>85.93734701901739</v>
       </c>
       <c r="C9" t="n">
-        <v>41.3768983970467</v>
+        <v>41.90656083737351</v>
       </c>
       <c r="D9" t="n">
-        <v>1.871685391908144</v>
+        <v>1.898618151348781</v>
       </c>
       <c r="E9" t="n">
-        <v>9.868162608045317</v>
+        <v>9.966206104482053</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508250779221286</v>
+        <v>0.7508489964187419</v>
       </c>
       <c r="G9" t="n">
-        <v>28.96266305603665</v>
+        <v>29.36764499699211</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53795358441791</v>
+        <v>34.53905383526212</v>
       </c>
       <c r="I9" t="n">
-        <v>4.733907849997754</v>
+        <v>4.722168706896435</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692656737013303</v>
+        <v>4.692806227617137</v>
       </c>
       <c r="K9" t="n">
-        <v>14.58214569465878</v>
+        <v>14.06265298098262</v>
       </c>
       <c r="L9" t="n">
-        <v>43.88344994906559</v>
+        <v>43.8736683401994</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84249404077107</v>
+        <v>99.84288215855554</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.03349788848085</v>
+        <v>83.68173940124179</v>
       </c>
       <c r="C10" t="n">
-        <v>39.72646691844048</v>
+        <v>40.38356739631281</v>
       </c>
       <c r="D10" t="n">
-        <v>1.764836823488972</v>
+        <v>1.797572618189079</v>
       </c>
       <c r="E10" t="n">
-        <v>9.963350672369877</v>
+        <v>10.09268540807529</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520160211479771</v>
+        <v>0.7520278020335526</v>
       </c>
       <c r="G10" t="n">
-        <v>27.30927670247355</v>
+        <v>27.80468230001282</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59273697280693</v>
+        <v>34.59327889354341</v>
       </c>
       <c r="I10" t="n">
-        <v>3.951180564018697</v>
+        <v>3.941318616677925</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700100132174856</v>
+        <v>4.700173762709704</v>
       </c>
       <c r="K10" t="n">
-        <v>16.96650211151913</v>
+        <v>16.31826059875823</v>
       </c>
       <c r="L10" t="n">
-        <v>43.17553352976267</v>
+        <v>43.16700065195963</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86850255972229</v>
+        <v>99.86882864703065</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>80.51111647518992</v>
+        <v>81.2533629460725</v>
       </c>
       <c r="C11" t="n">
-        <v>37.81587388452537</v>
+        <v>38.56599703656894</v>
       </c>
       <c r="D11" t="n">
-        <v>1.65305648537321</v>
+        <v>1.689881322840727</v>
       </c>
       <c r="E11" t="n">
-        <v>9.88182123444858</v>
+        <v>10.0361837476851</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530425899608026</v>
+        <v>0.7530424541373849</v>
       </c>
       <c r="G11" t="n">
-        <v>25.57957560893873</v>
+        <v>26.13892358554467</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63995913819691</v>
+        <v>34.6399528903197</v>
       </c>
       <c r="I11" t="n">
-        <v>3.297145231016675</v>
+        <v>3.288863607186258</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706516187255017</v>
+        <v>4.706515338358656</v>
       </c>
       <c r="K11" t="n">
-        <v>19.48888352481007</v>
+        <v>18.74663705392751</v>
       </c>
       <c r="L11" t="n">
-        <v>42.58548757499737</v>
+        <v>42.57788483681805</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89024498433281</v>
+        <v>99.8905189273145</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>77.99556887601895</v>
+        <v>78.78101126357205</v>
       </c>
       <c r="C12" t="n">
-        <v>35.80988515719157</v>
+        <v>36.60246603981663</v>
       </c>
       <c r="D12" t="n">
-        <v>1.542827122597687</v>
+        <v>1.581376251186355</v>
       </c>
       <c r="E12" t="n">
-        <v>9.681355343562425</v>
+        <v>9.849090436473917</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539279001479801</v>
+        <v>0.7539167233562</v>
       </c>
       <c r="G12" t="n">
-        <v>23.87387447628502</v>
+        <v>24.4605774565692</v>
       </c>
       <c r="H12" t="n">
-        <v>34.68068340680708</v>
+        <v>34.68016927438519</v>
       </c>
       <c r="I12" t="n">
-        <v>2.75085125069389</v>
+        <v>2.743901600624932</v>
       </c>
       <c r="J12" t="n">
-        <v>4.712049375924876</v>
+        <v>4.711979520976251</v>
       </c>
       <c r="K12" t="n">
-        <v>22.00443112398102</v>
+        <v>21.21898873642796</v>
       </c>
       <c r="L12" t="n">
-        <v>42.09409635129916</v>
+        <v>42.08718790133357</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90841263247177</v>
+        <v>99.90864267757816</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>75.44850799913188</v>
+        <v>76.22563124493013</v>
       </c>
       <c r="C13" t="n">
-        <v>33.68698663941351</v>
+        <v>34.47067829347501</v>
       </c>
       <c r="D13" t="n">
-        <v>1.43231499926237</v>
+        <v>1.470255144815568</v>
       </c>
       <c r="E13" t="n">
-        <v>9.370333531924118</v>
+        <v>9.53848746361459</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546922352975829</v>
+        <v>0.7546713338778962</v>
       </c>
       <c r="G13" t="n">
-        <v>22.16379787601575</v>
+        <v>22.7417667513982</v>
       </c>
       <c r="H13" t="n">
-        <v>34.7158428236888</v>
+        <v>34.71488135838322</v>
       </c>
       <c r="I13" t="n">
-        <v>2.294700062333369</v>
+        <v>2.28887335610381</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716826470609893</v>
+        <v>4.716695836736853</v>
       </c>
       <c r="K13" t="n">
-        <v>24.55149200086811</v>
+        <v>23.77436875506986</v>
       </c>
       <c r="L13" t="n">
-        <v>41.68510882497687</v>
+        <v>41.67873346254888</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92358746525849</v>
+        <v>99.92378051109375</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>82.64990661706558</v>
+        <v>83.16048414561318</v>
       </c>
       <c r="C14" t="n">
-        <v>38.14992921436832</v>
+        <v>38.88027917818246</v>
       </c>
       <c r="D14" t="n">
-        <v>1.434051864536537</v>
+        <v>1.471907777821707</v>
       </c>
       <c r="E14" t="n">
-        <v>11.84933576198753</v>
+        <v>11.97290762402975</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7556073962341415</v>
+        <v>0.7555196184491499</v>
       </c>
       <c r="G14" t="n">
-        <v>24.15719586400654</v>
+        <v>24.72364734292721</v>
       </c>
       <c r="H14" t="n">
-        <v>36.72446177285129</v>
+        <v>36.71022027002461</v>
       </c>
       <c r="I14" t="n">
-        <v>3.006707730986146</v>
+        <v>2.804283897053582</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722546226463384</v>
+        <v>4.721997615307188</v>
       </c>
       <c r="K14" t="n">
-        <v>17.35009338293444</v>
+        <v>16.8395158543868</v>
       </c>
       <c r="L14" t="n">
-        <v>44.39987519840025</v>
+        <v>44.18683379093697</v>
       </c>
       <c r="M14" t="n">
-        <v>99.899897795703</v>
+        <v>99.90662882350622</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>81.84283146435834</v>
+        <v>82.35169093442352</v>
       </c>
       <c r="C15" t="n">
-        <v>37.80671403002783</v>
+        <v>38.50467302662894</v>
       </c>
       <c r="D15" t="n">
-        <v>1.404572565216016</v>
+        <v>1.44208198838123</v>
       </c>
       <c r="E15" t="n">
-        <v>12.02377802380568</v>
+        <v>12.12014898729479</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7563792724990538</v>
+        <v>0.7562349439335986</v>
       </c>
       <c r="G15" t="n">
-        <v>23.6606048931844</v>
+        <v>24.22266330645309</v>
       </c>
       <c r="H15" t="n">
-        <v>36.76197694346161</v>
+        <v>36.74497748275294</v>
       </c>
       <c r="I15" t="n">
-        <v>2.508149313072486</v>
+        <v>2.339115826022879</v>
       </c>
       <c r="J15" t="n">
-        <v>4.727370453119086</v>
+        <v>4.726468399584992</v>
       </c>
       <c r="K15" t="n">
-        <v>18.15716853564166</v>
+        <v>17.64830906557645</v>
       </c>
       <c r="L15" t="n">
-        <v>43.95259777513647</v>
+        <v>43.76912113287645</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91648034080596</v>
+        <v>99.92210322508186</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>79.3011750153567</v>
+        <v>79.84630024561682</v>
       </c>
       <c r="C16" t="n">
-        <v>35.6520323769636</v>
+        <v>36.36061573531472</v>
       </c>
       <c r="D16" t="n">
-        <v>1.30946953547513</v>
+        <v>1.347558911994044</v>
       </c>
       <c r="E16" t="n">
-        <v>11.55831335753711</v>
+        <v>11.65086037317208</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7570443811616964</v>
+        <v>0.7568508361621539</v>
       </c>
       <c r="G16" t="n">
-        <v>22.05855508346324</v>
+        <v>22.63495839614694</v>
       </c>
       <c r="H16" t="n">
-        <v>36.79430293415168</v>
+        <v>36.77490329648531</v>
       </c>
       <c r="I16" t="n">
-        <v>2.091962341307272</v>
+        <v>1.950850705642821</v>
       </c>
       <c r="J16" t="n">
-        <v>4.731527382260602</v>
+        <v>4.730317726013463</v>
       </c>
       <c r="K16" t="n">
-        <v>20.69882498464327</v>
+        <v>20.15369975438318</v>
       </c>
       <c r="L16" t="n">
-        <v>43.5794718241411</v>
+        <v>43.42070907069034</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93032918574798</v>
+        <v>99.93502456038823</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.22852247338</v>
+        <v>81.63500529284636</v>
       </c>
       <c r="C17" t="n">
-        <v>37.03942782956093</v>
+        <v>37.66480704703679</v>
       </c>
       <c r="D17" t="n">
-        <v>1.310593436171168</v>
+        <v>1.34861833603865</v>
       </c>
       <c r="E17" t="n">
-        <v>12.42113184663555</v>
+        <v>12.45825988535789</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7576941425222088</v>
+        <v>0.7574458572531606</v>
       </c>
       <c r="G17" t="n">
-        <v>22.58179886410201</v>
+        <v>23.13009429139933</v>
       </c>
       <c r="H17" t="n">
-        <v>37.33019421579554</v>
+        <v>37.28115573549955</v>
       </c>
       <c r="I17" t="n">
-        <v>2.091521577389706</v>
+        <v>1.925394579465512</v>
       </c>
       <c r="J17" t="n">
-        <v>4.735588390763804</v>
+        <v>4.734036607832255</v>
       </c>
       <c r="K17" t="n">
-        <v>18.77147752662001</v>
+        <v>18.36499470715366</v>
       </c>
       <c r="L17" t="n">
-        <v>44.11943704411923</v>
+        <v>43.90606884375587</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93034240030018</v>
+        <v>99.93587059794631</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>78.77332854469141</v>
+        <v>79.1893343168889</v>
       </c>
       <c r="C18" t="n">
-        <v>34.90651346871314</v>
+        <v>35.5161633079063</v>
       </c>
       <c r="D18" t="n">
-        <v>1.22288481065303</v>
+        <v>1.260174714641411</v>
       </c>
       <c r="E18" t="n">
-        <v>11.88057802674039</v>
+        <v>11.90883247530767</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7582533783741631</v>
+        <v>0.7579577695487371</v>
       </c>
       <c r="G18" t="n">
-        <v>21.07056091232062</v>
+        <v>21.61320159631711</v>
       </c>
       <c r="H18" t="n">
-        <v>37.35774673572976</v>
+        <v>37.30635183609413</v>
       </c>
       <c r="I18" t="n">
-        <v>1.744221066034921</v>
+        <v>1.605579865300243</v>
       </c>
       <c r="J18" t="n">
-        <v>4.739083614838519</v>
+        <v>4.737236059679608</v>
       </c>
       <c r="K18" t="n">
-        <v>21.2266714553086</v>
+        <v>20.81066568311106</v>
       </c>
       <c r="L18" t="n">
-        <v>43.80871725438409</v>
+        <v>43.61968782621973</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94190217840583</v>
+        <v>99.9465168172371</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>77.85747574635361</v>
+        <v>78.18830508773071</v>
       </c>
       <c r="C19" t="n">
-        <v>34.25627633703635</v>
+        <v>34.75160092271946</v>
       </c>
       <c r="D19" t="n">
-        <v>1.190754309997598</v>
+        <v>1.224167392127822</v>
       </c>
       <c r="E19" t="n">
-        <v>11.81121509039416</v>
+        <v>11.79338348604181</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7587262872994786</v>
+        <v>0.7583936612148884</v>
       </c>
       <c r="G19" t="n">
-        <v>20.51694566965348</v>
+        <v>20.99564157754523</v>
       </c>
       <c r="H19" t="n">
-        <v>37.38104608706121</v>
+        <v>37.3278062343643</v>
       </c>
       <c r="I19" t="n">
-        <v>1.456749006325947</v>
+        <v>1.348952353843614</v>
       </c>
       <c r="J19" t="n">
-        <v>4.742039295621741</v>
+        <v>4.739960382593054</v>
       </c>
       <c r="K19" t="n">
-        <v>22.14252425364637</v>
+        <v>21.81169491226928</v>
       </c>
       <c r="L19" t="n">
-        <v>43.5526713751641</v>
+        <v>43.39176493051971</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95147196584682</v>
+        <v>99.95506076550845</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>75.25137737804525</v>
+        <v>75.61473202086405</v>
       </c>
       <c r="C20" t="n">
-        <v>31.87386923991496</v>
+        <v>32.38536754365246</v>
       </c>
       <c r="D20" t="n">
-        <v>1.098763908801978</v>
+        <v>1.132103045072811</v>
       </c>
       <c r="E20" t="n">
-        <v>11.10118789897859</v>
+        <v>11.09390138785576</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7591344999931137</v>
+        <v>0.7587696697079951</v>
       </c>
       <c r="G20" t="n">
-        <v>18.93193182791146</v>
+        <v>19.41664997454401</v>
       </c>
       <c r="H20" t="n">
-        <v>37.4011579742721</v>
+        <v>37.34631320889607</v>
       </c>
       <c r="I20" t="n">
-        <v>1.214610643131059</v>
+        <v>1.124684299112441</v>
       </c>
       <c r="J20" t="n">
-        <v>4.74459062495696</v>
+        <v>4.742310435674971</v>
       </c>
       <c r="K20" t="n">
-        <v>24.74862262195474</v>
+        <v>24.38526797913595</v>
       </c>
       <c r="L20" t="n">
-        <v>43.33704288795458</v>
+        <v>43.1918935784937</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95953474982427</v>
+        <v>99.96252910128212</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.4727125798573</v>
+        <v>81.59370316692868</v>
       </c>
       <c r="C21" t="n">
-        <v>35.76002914789593</v>
+        <v>36.18517927038078</v>
       </c>
       <c r="D21" t="n">
-        <v>1.099536922464264</v>
+        <v>1.132798687930669</v>
       </c>
       <c r="E21" t="n">
-        <v>13.18816070727399</v>
+        <v>13.11910046715726</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7596685740879273</v>
+        <v>0.7592359105716592</v>
       </c>
       <c r="G21" t="n">
-        <v>20.73782120679901</v>
+        <v>21.19627889583814</v>
       </c>
       <c r="H21" t="n">
-        <v>39.22004101269707</v>
+        <v>39.13695936243514</v>
       </c>
       <c r="I21" t="n">
-        <v>1.719555568485502</v>
+        <v>1.504105401922942</v>
       </c>
       <c r="J21" t="n">
-        <v>4.747928588049545</v>
+        <v>4.745224441072872</v>
       </c>
       <c r="K21" t="n">
-        <v>18.5272874201427</v>
+        <v>18.40629683307133</v>
       </c>
       <c r="L21" t="n">
-        <v>45.65540520997445</v>
+        <v>45.3584178384645</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94272177801307</v>
+        <v>99.94989394191661</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_10_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_10_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.24654833930718</v>
+        <v>43.87351746843122</v>
       </c>
       <c r="M2" t="n">
-        <v>99.56538375461344</v>
+        <v>93.70786227127985</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.04043937538745</v>
+        <v>81.38962295787239</v>
       </c>
       <c r="C3" t="n">
-        <v>45.93622173675656</v>
+        <v>43.14517851342795</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228758577077292</v>
+        <v>2.175728985818846</v>
       </c>
       <c r="E3" t="n">
-        <v>5.711361967982151</v>
+        <v>4.138417280786315</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429195256924307</v>
+        <v>0.7375713183670607</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97560501021501</v>
+        <v>32.72659016169182</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17429818185181</v>
+        <v>33.92828064488479</v>
       </c>
       <c r="I3" t="n">
-        <v>6.564249076991062</v>
+        <v>3.07321382652942</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643247035577692</v>
+        <v>4.609820739794129</v>
       </c>
       <c r="K3" t="n">
-        <v>11.95956062461255</v>
+        <v>18.61037704212761</v>
       </c>
       <c r="L3" t="n">
-        <v>48.86859771480408</v>
+        <v>45.13333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7643800761732</v>
+        <v>106.8888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.15020295939433</v>
+        <v>88.43015881795405</v>
       </c>
       <c r="C4" t="n">
-        <v>42.68010992566696</v>
+        <v>42.74188367081662</v>
       </c>
       <c r="D4" t="n">
-        <v>2.18599625133962</v>
+        <v>2.181418740438</v>
       </c>
       <c r="E4" t="n">
-        <v>6.515393052263231</v>
+        <v>6.515546889605339</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444771600807732</v>
+        <v>0.7395001430704071</v>
       </c>
       <c r="G4" t="n">
-        <v>33.32372826433323</v>
+        <v>33.41719231061573</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24594936371557</v>
+        <v>34.01700658123873</v>
       </c>
       <c r="I4" t="n">
-        <v>5.481676617157071</v>
+        <v>6.937618258795817</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652982250504833</v>
+        <v>4.621875894190044</v>
       </c>
       <c r="K4" t="n">
-        <v>12.84979704060568</v>
+        <v>11.56984118204594</v>
       </c>
       <c r="L4" t="n">
-        <v>44.28775278158872</v>
+        <v>45.4576243806065</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81765974786136</v>
+        <v>99.76934923346907</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.99652855293651</v>
+        <v>87.14675426473164</v>
       </c>
       <c r="C5" t="n">
-        <v>42.3772642961642</v>
+        <v>42.5338116220065</v>
       </c>
       <c r="D5" t="n">
-        <v>2.129757267497589</v>
+        <v>2.119628500515006</v>
       </c>
       <c r="E5" t="n">
-        <v>7.110466388594553</v>
+        <v>7.296682956141485</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457976984642514</v>
+        <v>0.7411390578921545</v>
       </c>
       <c r="G5" t="n">
-        <v>32.46641086762424</v>
+        <v>32.47062653113078</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30669412935556</v>
+        <v>34.0923966630391</v>
       </c>
       <c r="I5" t="n">
-        <v>4.576166585998744</v>
+        <v>5.794161444187172</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661235615401571</v>
+        <v>4.632119111825965</v>
       </c>
       <c r="K5" t="n">
-        <v>14.00347144706348</v>
+        <v>12.85324573526833</v>
       </c>
       <c r="L5" t="n">
-        <v>43.4669954618513</v>
+        <v>44.42023102442528</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84773120507899</v>
+        <v>99.80728838170012</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.66295688564968</v>
+        <v>85.64302616190591</v>
       </c>
       <c r="C6" t="n">
-        <v>41.75443924739364</v>
+        <v>41.92909358787965</v>
       </c>
       <c r="D6" t="n">
-        <v>2.064758271034725</v>
+        <v>2.047382138734954</v>
       </c>
       <c r="E6" t="n">
-        <v>7.529993351334759</v>
+        <v>7.854239413779959</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469191473541587</v>
+        <v>0.7425345028962186</v>
       </c>
       <c r="G6" t="n">
-        <v>31.47555422994453</v>
+        <v>31.36388323577357</v>
       </c>
       <c r="H6" t="n">
-        <v>34.3582807782913</v>
+        <v>34.15658713322605</v>
       </c>
       <c r="I6" t="n">
-        <v>3.819206436726723</v>
+        <v>4.837559094393782</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668244670963491</v>
+        <v>4.640840643101365</v>
       </c>
       <c r="K6" t="n">
-        <v>15.3370431143503</v>
+        <v>14.35697383809411</v>
       </c>
       <c r="L6" t="n">
-        <v>42.78140189975609</v>
+        <v>43.55298364502104</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87288426150005</v>
+        <v>99.8390510709948</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.08793117410553</v>
+        <v>84.02058701238018</v>
       </c>
       <c r="C7" t="n">
-        <v>40.77264462655828</v>
+        <v>41.05748334921365</v>
       </c>
       <c r="D7" t="n">
-        <v>1.988114304554906</v>
+        <v>1.970035788814508</v>
       </c>
       <c r="E7" t="n">
-        <v>7.781602981770919</v>
+        <v>8.230480116005845</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478740545238338</v>
+        <v>0.7437239629071556</v>
       </c>
       <c r="G7" t="n">
-        <v>30.30717953099023</v>
+        <v>30.17901313178943</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40220650809636</v>
+        <v>34.21130229372915</v>
       </c>
       <c r="I7" t="n">
-        <v>3.186740953395325</v>
+        <v>4.037756950964369</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674212840773961</v>
+        <v>4.648274768169721</v>
       </c>
       <c r="K7" t="n">
-        <v>16.91206882589447</v>
+        <v>15.97941298761984</v>
       </c>
       <c r="L7" t="n">
-        <v>42.20919747986039</v>
+        <v>42.82872702165556</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89391093231313</v>
+        <v>99.86562335848905</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.00852151280802</v>
+        <v>82.2736296301489</v>
       </c>
       <c r="C8" t="n">
-        <v>43.09981302519947</v>
+        <v>39.93709519380852</v>
       </c>
       <c r="D8" t="n">
-        <v>1.992373458864608</v>
+        <v>1.887378238525885</v>
       </c>
       <c r="E8" t="n">
-        <v>9.632453256509477</v>
+        <v>8.446715824918185</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494762315189604</v>
+        <v>0.7447392321931012</v>
       </c>
       <c r="G8" t="n">
-        <v>30.81784317704882</v>
+        <v>28.91278065532106</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47590664987217</v>
+        <v>34.25800468088264</v>
       </c>
       <c r="I8" t="n">
-        <v>5.656242292000476</v>
+        <v>3.369390797101151</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684226446993502</v>
+        <v>4.654620201206882</v>
       </c>
       <c r="K8" t="n">
-        <v>11.99147848719198</v>
+        <v>17.72637036985109</v>
       </c>
       <c r="L8" t="n">
-        <v>44.72057012829442</v>
+        <v>42.22437452103584</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81186164068586</v>
+        <v>99.88784008469545</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.93734701901739</v>
+        <v>80.47656843684224</v>
       </c>
       <c r="C9" t="n">
-        <v>41.90656083737351</v>
+        <v>38.66252370169338</v>
       </c>
       <c r="D9" t="n">
-        <v>1.898618151348781</v>
+        <v>1.803054698633433</v>
       </c>
       <c r="E9" t="n">
-        <v>9.966206104482053</v>
+        <v>8.537852617258102</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508489964187419</v>
+        <v>0.7456063718450355</v>
       </c>
       <c r="G9" t="n">
-        <v>29.36764499699211</v>
+        <v>27.62102685461238</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53905383526212</v>
+        <v>34.29789310487162</v>
       </c>
       <c r="I9" t="n">
-        <v>4.722168706896435</v>
+        <v>2.811094965590196</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692806227617137</v>
+        <v>4.660039824031471</v>
       </c>
       <c r="K9" t="n">
-        <v>14.06265298098262</v>
+        <v>19.52343156315776</v>
       </c>
       <c r="L9" t="n">
-        <v>43.8736683401994</v>
+        <v>41.72045054634049</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84288215855554</v>
+        <v>99.90640581119163</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.68173940124179</v>
+        <v>85.61721941819746</v>
       </c>
       <c r="C10" t="n">
-        <v>40.38356739631281</v>
+        <v>42.08751091386042</v>
       </c>
       <c r="D10" t="n">
-        <v>1.797572618189079</v>
+        <v>1.805186656041028</v>
       </c>
       <c r="E10" t="n">
-        <v>10.09268540807529</v>
+        <v>10.49301887479216</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520278020335526</v>
+        <v>0.746487987377171</v>
       </c>
       <c r="G10" t="n">
-        <v>27.80468230001282</v>
+        <v>29.09258226452955</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59327889354341</v>
+        <v>35.77734333599003</v>
       </c>
       <c r="I10" t="n">
-        <v>3.941318616677925</v>
+        <v>3.037050378360217</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700173762709704</v>
+        <v>4.665549921107318</v>
       </c>
       <c r="K10" t="n">
-        <v>16.31826059875823</v>
+        <v>14.38278058180254</v>
       </c>
       <c r="L10" t="n">
-        <v>43.16700065195963</v>
+        <v>43.42859305206763</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86882864703065</v>
+        <v>99.89888454773057</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.2533629460725</v>
+        <v>85.47212692498684</v>
       </c>
       <c r="C11" t="n">
-        <v>38.56599703656894</v>
+        <v>42.33559974269515</v>
       </c>
       <c r="D11" t="n">
-        <v>1.689881322840727</v>
+        <v>1.793830567127338</v>
       </c>
       <c r="E11" t="n">
-        <v>10.0361837476851</v>
+        <v>10.89181386217969</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530424541373849</v>
+        <v>0.7472375855331684</v>
       </c>
       <c r="G11" t="n">
-        <v>26.13892358554467</v>
+        <v>28.94522971470108</v>
       </c>
       <c r="H11" t="n">
-        <v>34.6399528903197</v>
+        <v>35.84893314235084</v>
       </c>
       <c r="I11" t="n">
-        <v>3.288863607186258</v>
+        <v>2.57484714351241</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706515338358656</v>
+        <v>4.670234909582302</v>
       </c>
       <c r="K11" t="n">
-        <v>18.74663705392751</v>
+        <v>14.52787307501317</v>
       </c>
       <c r="L11" t="n">
-        <v>42.57788483681805</v>
+        <v>43.05078504354951</v>
       </c>
       <c r="M11" t="n">
-        <v>99.8905189273145</v>
+        <v>99.91425786125784</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>78.78101126357205</v>
+        <v>83.78289255515159</v>
       </c>
       <c r="C12" t="n">
-        <v>36.60246603981663</v>
+        <v>41.04649501852722</v>
       </c>
       <c r="D12" t="n">
-        <v>1.581376251186355</v>
+        <v>1.722513705773</v>
       </c>
       <c r="E12" t="n">
-        <v>9.849090436473917</v>
+        <v>10.81671402419889</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539167233562</v>
+        <v>0.7478760301292587</v>
       </c>
       <c r="G12" t="n">
-        <v>24.4605774565692</v>
+        <v>27.794461647604</v>
       </c>
       <c r="H12" t="n">
-        <v>34.68016927438519</v>
+        <v>35.87956270125346</v>
       </c>
       <c r="I12" t="n">
-        <v>2.743901600624932</v>
+        <v>2.147539257885119</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711979520976251</v>
+        <v>4.674225188307866</v>
       </c>
       <c r="K12" t="n">
-        <v>21.21898873642796</v>
+        <v>16.21710744484841</v>
       </c>
       <c r="L12" t="n">
-        <v>42.08718790133357</v>
+        <v>42.66487400486015</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90864267757816</v>
+        <v>99.92847646823577</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76.22563124493013</v>
+        <v>85.13494567596324</v>
       </c>
       <c r="C13" t="n">
-        <v>34.47067829347501</v>
+        <v>42.13678104588337</v>
       </c>
       <c r="D13" t="n">
-        <v>1.470255144815568</v>
+        <v>1.723875535914844</v>
       </c>
       <c r="E13" t="n">
-        <v>9.53848746361459</v>
+        <v>11.52156129065272</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546713338778962</v>
+        <v>0.7484673056104226</v>
       </c>
       <c r="G13" t="n">
-        <v>22.7417667513982</v>
+        <v>28.17619051714217</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71488135838322</v>
+        <v>36.2676837024059</v>
       </c>
       <c r="I13" t="n">
-        <v>2.28887335610381</v>
+        <v>2.01924666417204</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716695836736853</v>
+        <v>4.677920660065141</v>
       </c>
       <c r="K13" t="n">
-        <v>23.77436875506986</v>
+        <v>14.86505432403674</v>
       </c>
       <c r="L13" t="n">
-        <v>41.67873346254888</v>
+        <v>42.93090958020516</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92378051109375</v>
+        <v>99.93274495012528</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.16048414561318</v>
+        <v>83.40644139795815</v>
       </c>
       <c r="C14" t="n">
-        <v>38.88027917818246</v>
+        <v>40.7220412968945</v>
       </c>
       <c r="D14" t="n">
-        <v>1.471907777821707</v>
+        <v>1.653050715560751</v>
       </c>
       <c r="E14" t="n">
-        <v>11.97290762402975</v>
+        <v>11.32884164907189</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555196184491499</v>
+        <v>0.7489709827889109</v>
       </c>
       <c r="G14" t="n">
-        <v>24.72364734292721</v>
+        <v>27.01858163525716</v>
       </c>
       <c r="H14" t="n">
-        <v>36.71022027002461</v>
+        <v>36.29208985142618</v>
       </c>
       <c r="I14" t="n">
-        <v>2.804283897053582</v>
+        <v>1.683837921422566</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721997615307188</v>
+        <v>4.681068642430692</v>
       </c>
       <c r="K14" t="n">
-        <v>16.8395158543868</v>
+        <v>16.59355860204185</v>
       </c>
       <c r="L14" t="n">
-        <v>44.18683379093697</v>
+        <v>42.62830991594775</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90662882350622</v>
+        <v>99.94390981488408</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.35169093442352</v>
+        <v>82.73414057008995</v>
       </c>
       <c r="C15" t="n">
-        <v>38.50467302662894</v>
+        <v>40.29050127782875</v>
       </c>
       <c r="D15" t="n">
-        <v>1.44208198838123</v>
+        <v>1.625214898513986</v>
       </c>
       <c r="E15" t="n">
-        <v>12.12014898729479</v>
+        <v>11.37538500836703</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7562349439335986</v>
+        <v>0.7494006448095875</v>
       </c>
       <c r="G15" t="n">
-        <v>24.22266330645309</v>
+        <v>26.56361416923662</v>
       </c>
       <c r="H15" t="n">
-        <v>36.74497748275294</v>
+        <v>36.31290952671196</v>
       </c>
       <c r="I15" t="n">
-        <v>2.339115826022879</v>
+        <v>1.423862292390846</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726468399584992</v>
+        <v>4.68375403005992</v>
       </c>
       <c r="K15" t="n">
-        <v>17.64830906557645</v>
+        <v>17.26585942991006</v>
       </c>
       <c r="L15" t="n">
-        <v>43.76912113287645</v>
+        <v>42.39620442779654</v>
       </c>
       <c r="M15" t="n">
-        <v>99.92210322508186</v>
+        <v>99.95256513553534</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>79.84630024561682</v>
+        <v>80.64551159921302</v>
       </c>
       <c r="C16" t="n">
-        <v>36.36061573531472</v>
+        <v>38.42274440177125</v>
       </c>
       <c r="D16" t="n">
-        <v>1.347558911994044</v>
+        <v>1.540173764645349</v>
       </c>
       <c r="E16" t="n">
-        <v>11.65086037317208</v>
+        <v>10.97801132682321</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7568508361621539</v>
+        <v>0.7497683606989769</v>
       </c>
       <c r="G16" t="n">
-        <v>22.63495839614694</v>
+        <v>25.17364422085232</v>
       </c>
       <c r="H16" t="n">
-        <v>36.77490329648531</v>
+        <v>36.33072754423759</v>
       </c>
       <c r="I16" t="n">
-        <v>1.950850705642821</v>
+        <v>1.187134127586971</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730317726013463</v>
+        <v>4.686052254368604</v>
       </c>
       <c r="K16" t="n">
-        <v>20.15369975438318</v>
+        <v>19.35448840078698</v>
       </c>
       <c r="L16" t="n">
-        <v>43.42070907069034</v>
+        <v>42.18321546709759</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93502456038823</v>
+        <v>99.96044826965581</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.63500529284636</v>
+        <v>85.12300762387963</v>
       </c>
       <c r="C17" t="n">
-        <v>37.66480704703679</v>
+        <v>41.32951638635453</v>
       </c>
       <c r="D17" t="n">
-        <v>1.34861833603865</v>
+        <v>1.541020340584175</v>
       </c>
       <c r="E17" t="n">
-        <v>12.45825988535789</v>
+        <v>12.54577091376825</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7574458572531606</v>
+        <v>0.7501804803366642</v>
       </c>
       <c r="G17" t="n">
-        <v>23.13009429139933</v>
+        <v>26.5152619417136</v>
       </c>
       <c r="H17" t="n">
-        <v>37.28115573549955</v>
+        <v>37.6784778966927</v>
       </c>
       <c r="I17" t="n">
-        <v>1.925394579465512</v>
+        <v>1.403668048680071</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734036607832255</v>
+        <v>4.688628002104149</v>
       </c>
       <c r="K17" t="n">
-        <v>18.36499470715366</v>
+        <v>14.87699237612038</v>
       </c>
       <c r="L17" t="n">
-        <v>43.90606884375587</v>
+        <v>43.74672800656891</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93587059794631</v>
+        <v>99.95323676904381</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.1893343168889</v>
+        <v>86.84944041422875</v>
       </c>
       <c r="C18" t="n">
-        <v>35.5161633079063</v>
+        <v>42.10125352411383</v>
       </c>
       <c r="D18" t="n">
-        <v>1.260174714641411</v>
+        <v>1.542384415045068</v>
       </c>
       <c r="E18" t="n">
-        <v>11.90883247530767</v>
+        <v>13.18479312882975</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7579577695487371</v>
+        <v>0.7508445222103098</v>
       </c>
       <c r="G18" t="n">
-        <v>21.61320159631711</v>
+        <v>26.66049848377221</v>
       </c>
       <c r="H18" t="n">
-        <v>37.30635183609413</v>
+        <v>37.71182998690892</v>
       </c>
       <c r="I18" t="n">
-        <v>1.605579865300243</v>
+        <v>2.306311613648058</v>
       </c>
       <c r="J18" t="n">
-        <v>4.737236059679608</v>
+        <v>4.692778263814435</v>
       </c>
       <c r="K18" t="n">
-        <v>20.81066568311106</v>
+        <v>13.15055958577124</v>
       </c>
       <c r="L18" t="n">
-        <v>43.61968782621973</v>
+        <v>44.67137782587888</v>
       </c>
       <c r="M18" t="n">
-        <v>99.9465168172371</v>
+        <v>99.92319093576394</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.18830508773071</v>
+        <v>84.54324633461374</v>
       </c>
       <c r="C19" t="n">
-        <v>34.75160092271946</v>
+        <v>40.1526475276934</v>
       </c>
       <c r="D19" t="n">
-        <v>1.224167392127822</v>
+        <v>1.457544524858363</v>
       </c>
       <c r="E19" t="n">
-        <v>11.79338348604181</v>
+        <v>12.78011870227196</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7583936612148884</v>
+        <v>0.7514139200318593</v>
       </c>
       <c r="G19" t="n">
-        <v>20.99564157754523</v>
+        <v>25.19401986688347</v>
       </c>
       <c r="H19" t="n">
-        <v>37.3278062343643</v>
+        <v>37.74042849592911</v>
       </c>
       <c r="I19" t="n">
-        <v>1.348952353843614</v>
+        <v>1.923383824439846</v>
       </c>
       <c r="J19" t="n">
-        <v>4.739960382593054</v>
+        <v>4.696337000199119</v>
       </c>
       <c r="K19" t="n">
-        <v>21.81169491226928</v>
+        <v>15.45675366538629</v>
       </c>
       <c r="L19" t="n">
-        <v>43.39176493051971</v>
+        <v>44.32653459543007</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95506076550845</v>
+        <v>99.93593578850975</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>75.61473202086405</v>
+        <v>82.03567616590354</v>
       </c>
       <c r="C20" t="n">
-        <v>32.38536754365246</v>
+        <v>37.94266348761881</v>
       </c>
       <c r="D20" t="n">
-        <v>1.132103045072811</v>
+        <v>1.36574469095015</v>
       </c>
       <c r="E20" t="n">
-        <v>11.09390138785576</v>
+        <v>12.24250529517102</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7587696697079951</v>
+        <v>0.751903611872248</v>
       </c>
       <c r="G20" t="n">
-        <v>19.41664997454401</v>
+        <v>23.60723689057277</v>
       </c>
       <c r="H20" t="n">
-        <v>37.34631320889607</v>
+        <v>37.76502370157349</v>
       </c>
       <c r="I20" t="n">
-        <v>1.124684299112441</v>
+        <v>1.603864401562303</v>
       </c>
       <c r="J20" t="n">
-        <v>4.742310435674971</v>
+        <v>4.699397574201549</v>
       </c>
       <c r="K20" t="n">
-        <v>24.38526797913595</v>
+        <v>17.96432383409645</v>
       </c>
       <c r="L20" t="n">
-        <v>43.1918935784937</v>
+        <v>44.0395853498281</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96252910128212</v>
+        <v>99.94657267154338</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.59370316692868</v>
+        <v>79.53318163282437</v>
       </c>
       <c r="C21" t="n">
-        <v>36.18517927038078</v>
+        <v>35.68765490014842</v>
       </c>
       <c r="D21" t="n">
-        <v>1.132798687930669</v>
+        <v>1.274621423129973</v>
       </c>
       <c r="E21" t="n">
-        <v>13.11910046715726</v>
+        <v>11.64856212828748</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7592359105716592</v>
+        <v>0.7523250388244972</v>
       </c>
       <c r="G21" t="n">
-        <v>21.19627889583814</v>
+        <v>22.032148527478</v>
       </c>
       <c r="H21" t="n">
-        <v>39.13695936243514</v>
+        <v>37.78619024285469</v>
       </c>
       <c r="I21" t="n">
-        <v>1.504105401922942</v>
+        <v>1.337302779596613</v>
       </c>
       <c r="J21" t="n">
-        <v>4.745224441072872</v>
+        <v>4.702031492653107</v>
       </c>
       <c r="K21" t="n">
-        <v>18.40629683307133</v>
+        <v>20.46681836717566</v>
       </c>
       <c r="L21" t="n">
-        <v>45.3584178384645</v>
+        <v>43.80097494374363</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94989394191661</v>
+        <v>99.9554482110677</v>
       </c>
     </row>
   </sheetData>
